--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Cloud-Native Developer</t>
+          <t>Senior Full Stack AWS Engineer- Virtual</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0dab06dbe191608</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ab4655f4008598</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-4</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
+          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Java Cloud-Native Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,54 +671,54 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
+          <t>https://www.indeed.com/viewjob?jk=e0dab06dbe191608</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Python and PySpark, No SQL Developer-4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer Remote</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NuView</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Medallion Architecture, GCP, BigQuery, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa3e227f230a38e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0898e60057ca64e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=0898e60057ca64e0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,69 +1536,69 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73f9cbcb57b8893b</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,172 +3261,172 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Skidmore, Owings &amp; Merrill</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Snowflake, Data Modeling, ETL, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30cc04c7a5b1640</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Generative AI Architect</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c985542971e6d41d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,102 +3541,102 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,77 +3751,1932 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>Software Product Architect</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Software Product Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Product Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Product Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Architect (GCP, Snowflake)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Addepto</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Constitution Surgery Alliance</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Issaquah, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Issaquah, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Data Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Acosta Group</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Java Security Testing Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Data Engineer - DataBricks</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Sumitomo Group</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer III</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Data Architect - Hybrid</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TruStage</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Google Cloud Solution Architect</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Full Stack)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Peoria, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Developer (contract)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior API Engineer (Python / AWS)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Analytics &amp; AI Architect</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Vessco Water</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Chanhassen, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Product Analytics, Senior Associate</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Belfast, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior, Data Scientist</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Sr DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>San Ramon, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Informatica</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Data Engineer - Mid</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Crimson Phoenix</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Springfield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Broadridge</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Newark, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Informatica</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Mexico, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Data Engineer - Oklahoma City, OK</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CFS Brands, LLC</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Sherwin-Williams</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Data Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SimilarWeb</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Data Engineer - Sr. Consultant level</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Pismo</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Junior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ideacrew</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Data Analyst/Data Engineer (Healthcare)</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Priority Management</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Generative AI Architect</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Spark, PySpark</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c985542971e6d41d</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>GCP ML Architect</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Woven Health Collective</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Sr. Machine Learning/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Financial Independence Group</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Cornelius, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Sr Firmware DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Fort Smith, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>Product Analytics, Associate</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>athenahealth</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Belfast, ME, US USA</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D148" t="n">
         <v>10.4</v>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Sr AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ulta</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Bolingbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,52 +748,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a76b23bc92692fef</t>
+          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
         </is>
       </c>
     </row>
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=0898e60057ca64e0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0898e60057ca64e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,69 +1536,69 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
@@ -4743,12 +4743,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Analyst/Data Engineer (Healthcare)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Priority Management</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Snowflake, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8d1d17b6d68057</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Generative AI Architect</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,24 +5246,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c985542971e6d41d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Generative AI Architect</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=c985542971e6d41d</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Woven Health Collective</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c5820060bccb38</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (HYBRID)</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90453733877516a5</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr AI ML Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,155 +5526,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Summit Utilities, Inc.</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Product Analytics, Associate</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>athenahealth</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Belfast, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Sr AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Ulta</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Bolingbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Associate Technical Architect - DE - Databricks</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Redshift, Step Functions, S3, Databricks, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b314c9efdb4188c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,69 +1536,69 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,14 +4171,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Machine Learning Engineer III</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
         </is>
       </c>
     </row>
@@ -4743,12 +4743,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,24 +5106,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>Generative AI Architect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=c985542971e6d41d</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Woven Health Collective</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Generative AI Architect</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c985542971e6d41d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,15 +5526,50 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sr AI ML Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Ulta</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Bolingbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2148,7 +2148,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2176,14 +2176,14 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4318,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer III</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3b0859d9457f7e5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
@@ -4668,17 +4668,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
@@ -4743,12 +4743,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,24 +5106,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Technology Engineer - Java, Angular, React</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Kubernetes, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ebadb315e19ee162</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Generative AI Architect</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c985542971e6d41d</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
@@ -5298,17 +5298,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>Generative AI Architect</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=c985542971e6d41d</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>
       </c>
     </row>
@@ -5473,17 +5473,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr AI ML Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ulta</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Bolingbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr AI ML Engineer</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ulta</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bolingbrook, IL, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,17 +5561,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,95 +538,95 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, ECS, Azure, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d75692293d003a</t>
+          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack AWS Engineer- Virtual</t>
+          <t>Python and PySpark, No SQL Developer-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ab4655f4008598</t>
+          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Cloud-Native Developer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,77 +671,77 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0dab06dbe191608</t>
+          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-4</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,15 +1108,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineering Associate - Cloud Enablement &amp; Automation</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ab89045d08ef18</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Spark, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0898e60057ca64e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Technical Architect - DE - Databricks</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1497,46 +1497,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, S3, Databricks, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b314c9efdb4188c</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Infrastructure Engineer (Backend)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,42 +4301,42 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Texas Oncology</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,102 +4416,102 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b9e64510577fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b99631b1e6f2b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37f813b5cb175d0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,472 +5106,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Technology Engineer - Java, Angular, React</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Kubernetes, Jenkins, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebadb315e19ee162</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Financial Independence Group</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Cornelius, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Sr Firmware DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Woven Health Collective</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Generative AI Architect</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Spark, PySpark</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c985542971e6d41d</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Summit Utilities, Inc.</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Fort Smith, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Summit Utilities, Inc.</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Fayetteville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Summit Utilities, Inc.</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Santa Monica, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Sr AI ML Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Ulta</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Bolingbrook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Spark, Scala, MySQL, MongoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c97a6763a721f8de</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Product Analytics, Associate</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>athenahealth</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Belfast, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-4</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
+          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Python and PySpark, No SQL Developer-4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
+          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
+          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>GCP AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
+          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9275dfa105600f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbda2b1be4a20921</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer (Backend)</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, SQS, ECS, IAM, Azure, GCP, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0be821cc97d69bf4</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer - APIs</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
@@ -3898,52 +3898,52 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,24 +3951,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Texas Oncology</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Texas Oncology</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Software Engineer III - Data Protection &amp; Recovery</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Woven Health Collective</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,15 +5106,155 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Product Analytics, Associate</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Belfast, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>GCP ML Architect</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a4bbd6dc8ae1d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,69 +1361,69 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
@@ -1973,25 +1973,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734740ee36ff607d</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,94 +3821,94 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Texas Oncology</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Texas Oncology</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Data Protection &amp; Recovery</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Woven Health Collective</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5185,76 +5185,6 @@
         </is>
       </c>
       <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Product Analytics, Associate</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>athenahealth</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Belfast, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,42 +3821,42 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Texas Oncology</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Texas Oncology</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Software Engineer III - Data Protection &amp; Recovery</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Woven Health Collective</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,15 +5176,85 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Product Analytics, Associate</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Belfast, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>GCP ML Architect</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
+          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
@@ -1343,52 +1343,52 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
@@ -3828,35 +3828,35 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
+          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
@@ -4353,25 +4353,25 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Texas Oncology</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Texas Oncology</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - Data Protection &amp; Recovery</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Woven Health Collective</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5220,41 +5220,6 @@
         </is>
       </c>
       <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lynchburg, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5123,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>EMR, Redshift, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, Airflow</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1305647d227e74d0</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5185,41 +5185,6 @@
         </is>
       </c>
       <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
@@ -4038,17 +4038,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
+          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
+          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
@@ -4248,17 +4248,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
@@ -4913,17 +4913,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Woven Health Collective</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Smith, AR, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Summit Utilities, Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Product Analytics, Associate</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI &amp; Data Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd934ff3fd857de0</t>
+          <t>https://www.indeed.com/viewjob?jk=0e27010d95a9e3bd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd934ff3fd857de0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, EMR, Kinesis, Redshift, ECS, Azure, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
+          <t>https://www.indeed.com/viewjob?jk=62d75692293d003a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-4</t>
+          <t>Senior Full Stack AWS Engineer- Virtual</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ab4655f4008598</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
+          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Python and PySpark, No SQL Developer-4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,15 +1108,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,29 +1151,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=f51272f2fb3899cf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,54 +1441,54 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Associate Technical Architect - DE - Databricks</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1497,46 +1497,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Step Functions, S3, Databricks, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=4b314c9efdb4188c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lynchburg, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lynchburg, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Analytics Engineer II-Operations</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,102 +3821,102 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,49 +3996,49 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,42 +4371,42 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,137 +4416,137 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
+          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Texas Oncology</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
+          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Product Analytics, Senior Associate</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>Belfast, ME, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Texas Oncology</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Pismo</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Fort Smith, AR, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Fayetteville, AR, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Summit Utilities, Inc.</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Product Analytics, Associate</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Pismo</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Technology Engineer - Java, Angular, React</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Woven Health Collective</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Kubernetes, Jenkins, SonarQube, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=ebadb315e19ee162</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,15 +5176,330 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3aded09f63bb45f</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Sr Firmware DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Sr. Machine Learning/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Financial Independence Group</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Cornelius, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Fort Smith, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Summit Utilities, Inc.</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Product Analytics, Associate</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>athenahealth</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Belfast, ME, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>GCP ML Architect</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,200 +573,200 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, ECS, Azure, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d75692293d003a</t>
+          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack AWS Engineer- Virtual</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ab4655f4008598</t>
+          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>Python and PySpark, No SQL Developer-4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
+          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-4</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
+          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>GCP Trainee / Apprentice Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
+          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Gainwell Technologies LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,15 +1108,15 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51272f2fb3899cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Technical Architect - DE - Databricks</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, S3, Databricks, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b314c9efdb4188c</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6f9f9b97c543b71</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Behavioral Health Data Engineer (BH-DE)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,102 +3786,102 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Analytics Engineer II-Operations</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a67e9e9d00aefc4e</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,67 +3961,67 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,42 +4231,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,67 +4346,67 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,67 +4416,67 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,67 +4486,67 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Product Analytics, Senior Associate</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belfast, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e9aeecafcd087e</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,59 +4591,59 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Remote Senior Healthcare Data Engineer - Precision Medicine Informatics - Dallas, Tx</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Texas Oncology</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa8179ba2a6e67fe</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,29 +4721,29 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4800,706 +4800,6 @@
         </is>
       </c>
       <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Informatica</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Data Engineer - Mid</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Crimson Phoenix</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Springfield, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Broadridge</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Newark, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>CFS Brands, LLC</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Sherwin-Williams</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Data Engineer - Sr. Consultant level</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Pismo</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f47454da8e4e4715</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Junior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Ideacrew</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Technology Engineer - Java, Angular, React</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Kubernetes, Jenkins, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebadb315e19ee162</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Woven Health Collective</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Data Protection &amp; Recovery</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>ERP &amp; Database Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Missouri State University</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3aded09f63bb45f</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Sr Firmware DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Financial Independence Group</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Cornelius, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Summit Utilities, Inc.</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Fort Smith, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2fec50f02a5ef6aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Summit Utilities, Inc.</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Fayetteville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=faa9dfb3a4929603</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>AI Data Scientist</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Summit Utilities, Inc.</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Little Rock, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Snowflake, MLOps, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba51b0aca980bb32</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Product Analytics, Associate</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>athenahealth</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Belfast, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Athena, RDS, Spark, Scala, Snowflake, Data Modeling, Power BI, Tableau, CI/CD, AKS</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8191c9528fa3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd934ff3fd857de0</t>
+          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Python and PySpark, No SQL Developer-4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
+          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-4</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
+          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
+          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
+          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCP Trainee / Apprentice Engineer</t>
+          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Interclypse, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be354de203125f15</t>
+          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
+          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gainwell Technologies LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Databricks, Spark, Scala, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c9630e433b0cdaa</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,102 +1126,102 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90ae4f8d8427460d</t>
+          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c263a3534085da2</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e10e7c5992d07e</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c542148e5993d901</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>Data Developer - L2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Lynchburg, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd27eb8dc1015d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lynchburg, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Behavioral Health Data Engineer (BH-DE)</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Welfare Research Inc. d/b/a WRI Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72092efa1ab514ab</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Issaquah, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>AI/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Acosta Group</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,102 +3576,102 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,59 +3751,59 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Analytics &amp; AI Architect</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Vessco Water</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chanhassen, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Informatica</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf5fcb52918d331</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4695,111 +4695,6 @@
         </is>
       </c>
       <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Sr Firmware DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Woven Health Collective</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,52 +1693,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffcdaf2a52019fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Architect (GCP, Snowflake)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Addepto</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,102 +3401,102 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81d0fe049db3a5c5</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4966d5bf8d7c4665</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Issaquah, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5500cd01d24e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Acosta Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Dimension Tables, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116d2aae5d42caac</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Data Engineer - DataBricks</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,24 +3671,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
+          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,42 +3916,42 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Analytics &amp; AI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Vessco Water</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chanhassen, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Data Modeling, dbt, Power BI</t>
+          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5a01cb73725f2f</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,67 +4066,67 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
@@ -4183,12 +4183,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>SimilarWeb</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SimilarWeb</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4450,251 +4450,6 @@
         </is>
       </c>
       <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a087bbfc74bb05</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b283ba99e10e1ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Sr Firmware DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Woven Health Collective</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Financial Independence Group</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Cornelius, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,12 +853,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer (GCP, Snowflake)</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171e4e9a5f95f349</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,94 +986,94 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,104 +1081,104 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77a2037f942c65a</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Developer - L2</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c72f53b3836fad3b</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lynchburg, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Architect (GCP, Snowflake)</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Addepto</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a9ab76e83e7683</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,24 +3496,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer - DataBricks</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031d8aae1cb04c4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior, Data Scientist</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,59 +3891,59 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e347cfbf683cf04</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Data Engineer - Oklahoma City, OK</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>CFS Brands, LLC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>Ideacrew</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, MySQL, ETL, ELT, dbt, Tableau, Tableau Server, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd6703d1d75ffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4170,286 +4170,6 @@
         </is>
       </c>
       <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Sherwin-Williams</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Solution Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>SimilarWeb</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57dda46ad6b7a646</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Junior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Ideacrew</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Sr Firmware DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Woven Health Collective</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Financial Independence Group</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Cornelius, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,52 +993,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a391c3e6f726ee71</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,69 +1046,69 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1546,59 +1546,59 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,42 +3226,42 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,24 +3321,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,69 +3671,69 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Informatica</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer - Oklahoma City, OK</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CFS Brands, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb492a67fde6480</t>
+          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, MySQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b255fff754cbea82</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ideacrew</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe9de487ccd11ade</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4065,111 +4065,6 @@
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Woven Health Collective</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Financial Independence Group</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Cornelius, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7dc31395c5cbccb</t>
+          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555b9ede0754b52b</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94b575aa256e1ed7</t>
+          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer (HPC) Linux &amp; Scripting Emphasis</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Interclypse, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, Splunk</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a1bc49d1bd29ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff01e0919e5668ba</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=659e6db932cf230f</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,49 +1021,49 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,19 +1336,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,46 +1357,46 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>DuBois Chemicals</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Sharonville, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,137 +3016,137 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Sr Firmware DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3820,251 +3820,6 @@
         </is>
       </c>
       <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Informatica</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Mexico, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, EMR, S3, ECS, IAM, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eabefa51e4976b97</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Sr Firmware DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Woven Health Collective</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Financial Independence Group</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Cornelius, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,47 +468,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI &amp; Data Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>U.S. Pharmacopeia</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8ca3a4199bd053</t>
+          <t>https://www.indeed.com/viewjob?jk=0e27010d95a9e3bd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI &amp; Data Solution Architect</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Slalom Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,46 +517,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
+          <t>AWS, EMR, Kinesis, Redshift, ECS, Azure, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e27010d95a9e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=62d75692293d003a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>Senior Full Stack AWS Engineer- Virtual</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2ab4655f4008598</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
+          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-4</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
+          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Python and PySpark, No SQL Developer-4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, ETL, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a508ab92f1823a0</t>
+          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,29 +836,29 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Technical Architect - DE - Databricks</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Quantiphi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,73 +867,73 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, Step Functions, S3, Databricks, Spark, PySpark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=4b314c9efdb4188c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Sharonville, OH Corporate Headquarters</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DuBois Chemicals</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sharonville, OH, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Scala, Snowflake, Data Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9383d85a0eb4828</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
@@ -3023,35 +3023,35 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Java Security Testing Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, CI/CD, Jenkins, GitHub Actions, Terraform, AWS CloudFormation, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff42a068bdbef04</t>
+          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Full Stack)</t>
+          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
+          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,24 +3426,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
+          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3461,42 +3461,42 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer - Mid</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Crimson Phoenix</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Springfield, VA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
+          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr Firmware DevOps Engineer</t>
+          <t>Sr. Site Reliability Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Woven Health Collective</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Financial Independence Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cornelius, NC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Senior Technology Engineer - Java, Angular, React</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,15 +3811,190 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Kubernetes, Jenkins, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebadb315e19ee162</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Woven Health Collective</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Data Protection &amp; Recovery</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Sr Firmware DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sr. Machine Learning/AI Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Financial Independence Group</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Cornelius, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>GCP ML Architect</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>

--- a/results/job_matches_2026-03-28.xlsx
+++ b/results/job_matches_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,130 +503,130 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Sr. Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Slalom Consulting</t>
+          <t>Diversify</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, ECS, Azure, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d75692293d003a</t>
+          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full Stack AWS Engineer- Virtual</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2ab4655f4008598</t>
+          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Integrations Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diversify</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685f900cfcc4db8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f760910209d307d5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python and PySpark, No SQL Developer-4</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, MongoDB, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23d20f4c9bc6ff98</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, Dask, MLOps, MLflow, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,49 +706,49 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, API Gateway, ECS, RDS, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab1a7566b504833</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,50 +758,50 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413a6f7ee51cdacf</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Peraton</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a8e3179e23b63c6</t>
+          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086171f47946e79e</t>
+          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Technical Architect - DE - Databricks</t>
+          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quantiphi</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Step Functions, S3, Databricks, Spark, PySpark, Scala, Snowflake, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b314c9efdb4188c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Diversified</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958d4a0fb09fa9ae</t>
+          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f9878e43fea763</t>
+          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05cb80d44bbb04c</t>
+          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Analytics Data Modeler</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Genworth</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Glen Allen, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7586f5a67c700591</t>
+          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Microsoft Fabric Data Engineer</t>
+          <t>Application Developer, Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Dataflow, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db3afa4eaeaaefb8</t>
+          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Data Modeler</t>
+          <t>Application Developer, Senior</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Genworth</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Glen Allen, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f536a48f4fdc34</t>
+          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Application Developer, Experienced</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700838b5ae6d65cf</t>
+          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FULL-STACK PLATFORM ENGINEER - AGENTIC AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Peraton</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a008472239406dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IES ETL Developer (Project Assistant) ref# 10992</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b99d4dcee343631</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ca767522f03ad</t>
+          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Application Developer, Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94c803dbf4827b26</t>
+          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Application Developer, Senior</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>GigaTech</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3718b32eb6f37d75</t>
+          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Application Developer, Experienced</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c18363aa2c52f5</t>
+          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Product Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fef73349a43ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eb4db52397ef20c</t>
+          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fa954902b46c5d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333ae404dd34cbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ded58bcf667d917</t>
+          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b46e98c69893ca89</t>
+          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Huntsville, AL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd40b868a72be114</t>
+          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55fe46eb30bf558d</t>
+          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Huntsville, AL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be51ca09a12133f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f62f1d27d9bcc7</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1620f3048487508d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c7060ab605a6da6</t>
+          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed5f9dd6726dfa1</t>
+          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd881f9a9d80b357</t>
+          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf33ed75098ddba</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35cd794e31e1371b</t>
+          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b87e67f633a413</t>
+          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c63000378ccab9</t>
+          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc983dd47b6b4903</t>
+          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254fe941714812ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b5e714598120506</t>
+          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e569e5fed71aaa85</t>
+          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58e0c148a8771ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083af3bb92fb47e1</t>
+          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb07f515311c26f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372ba56cb0f4713e</t>
+          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5352ddc6938b45b</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=139d084c4035272f</t>
+          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb231ade4797f72</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee78dcb4ebbee99</t>
+          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc6fce23c5b4ed8</t>
+          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c5bde39d3c6eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c2464a99a3e0000</t>
+          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ca5e9ed10ce680</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19342b302bc8ed18</t>
+          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5329cf0676570e</t>
+          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c004ba57051a5fb9</t>
+          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e84d65b2b8cba0</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Product Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Constitution Surgery Alliance</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, MLOps, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92e8f04946c3d5f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3170bd3f141b51</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,84 +2876,84 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=909d897f2ba2cb33</t>
+          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc2e1aa6fd844906</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GigaTech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=624af1ebb09380d1</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,15 +2963,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c5155b5ac41196</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior API Engineer (Python / AWS)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Constitution Surgery Alliance</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a48717f3aef28ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Data Architect - Hybrid</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TruStage</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Java Full Stack Developer (contract)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior Software Engineer (Full Stack)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,24 +3181,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,50 +3208,50 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, RDS, Scala, Snowflake, Time Travel, Data Modeling</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e3a9a9d9c081ae</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Java Security Testing Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de18db0abdbbc63</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior API Engineer (Python / AWS)</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c681622c90cd160b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Data Engineer - Mid</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Crimson Phoenix</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Springfield, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Architect - Hybrid</t>
+          <t>Sr. Machine Learning/AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TruStage</t>
+          <t>Financial Independence Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cornelius, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,637 +3366,42 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e5afd28e9bafa56</t>
+          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Deep Learning &amp; GPU ML Serving</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Woven Health Collective</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Cassandra, NoSQL, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65af32e7dacb8cde</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Full Stack)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Peoria, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, SNS, ECS, RDS, Azure, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc2794850e208d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Java Full Stack Developer (contract)</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>BNY</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, Scala, Kafka, Snowflake, Oracle, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a196cc7b3dc6132</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Software Test Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Peoria, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Sr DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b3970815943cac3</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Engineer l</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>PepperPointe Partnerships</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Lexington, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Data Engineer - Mid</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Crimson Phoenix</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Springfield, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Glue, S3, RDS, Spark, Scala, Oracle, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c3206404a7cafe75</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Broadridge</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Newark, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4b0489f31a0619b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e88e8db10ef6f01</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Technology Engineer - Java, Angular, React</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Kafka, SQL Server, CI/CD, Jenkins, Kubernetes, Jenkins, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebadb315e19ee162</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Woven Health Collective</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins, AKS, Jenkins</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-02-24</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3d0fb7c97aeebb8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Data Protection &amp; Recovery</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a3ede6c693f79ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Sr Firmware DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Brookfield, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6171331838e8d021</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning/AI Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Financial Independence Group</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Cornelius, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, MLOps, MLflow, Python</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=639c100c6cc2a73a</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>GCP ML Architect</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce109653891dcb6c</t>
         </is>
       </c>
     </row>
